--- a/Output/Models/List_models_exposure_malf_card_bin.xlsx
+++ b/Output/Models/List_models_exposure_malf_card_bin.xlsx
@@ -646,7 +646,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -757,7 +757,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -794,7 +794,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -831,7 +831,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -905,7 +905,7 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -942,7 +942,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -979,7 +979,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -1016,7 +1016,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -1053,7 +1053,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1349,7 +1349,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1460,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -1571,7 +1571,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -1682,7 +1682,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -1719,7 +1719,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs</t>
+          <t>pct1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs</t>
+          <t>t1_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_cs</t>
+          <t>t2_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2089,7 +2089,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_cs</t>
+          <t>t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_cs</t>
+          <t>w20_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2163,7 +2163,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_cs</t>
+          <t>tot_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2200,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs</t>
+          <t>pct1_K_cs</t>
         </is>
       </c>
     </row>
@@ -2237,7 +2237,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs</t>
+          <t>t1_K_cs</t>
         </is>
       </c>
     </row>
@@ -2274,7 +2274,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>iqr_t2_K_cs</t>
+          <t>t2_K_cs</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2311,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>iqr_t3_K_cs</t>
+          <t>t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>iqr_w20_K_cs</t>
+          <t>w20_K_cs</t>
         </is>
       </c>
     </row>
@@ -2385,7 +2385,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>iqr_tot_K_cs</t>
+          <t>tot_K_cs</t>
         </is>
       </c>
     </row>
@@ -2644,7 +2644,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp</t>
+          <t>pct1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp</t>
+          <t>t1_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>iqr_t2_Levo_sp</t>
+          <t>t2_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2755,7 +2755,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>iqr_t3_Levo_sp</t>
+          <t>t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2792,7 +2792,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>iqr_w20_Levo_sp</t>
+          <t>w20_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2829,7 +2829,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>iqr_tot_Levo_sp</t>
+          <t>tot_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp</t>
+          <t>pct1_K_sp</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp</t>
+          <t>t1_K_sp</t>
         </is>
       </c>
     </row>
@@ -2940,7 +2940,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>iqr_t2_K_sp</t>
+          <t>t2_K_sp</t>
         </is>
       </c>
     </row>
@@ -2977,7 +2977,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>iqr_t3_K_sp</t>
+          <t>t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3014,7 +3014,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>iqr_w20_K_sp</t>
+          <t>w20_K_sp</t>
         </is>
       </c>
     </row>
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>iqr_tot_K_sp</t>
+          <t>tot_K_sp</t>
         </is>
       </c>
     </row>
@@ -3125,7 +3125,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3236,7 +3236,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3273,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_cs + iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>pct1_Levo_cs + t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3384,7 +3384,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_cs + iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>pct1_K_cs + t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3458,7 +3458,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>iqr_pct1_Levo_sp + iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>pct1_Levo_sp + t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3495,7 +3495,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>iqr_pct1_K_sp + iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>pct1_K_sp + t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3569,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3680,7 +3680,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3717,7 +3717,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_cs + iqr_t2_Levo_cs + iqr_t3_Levo_cs</t>
+          <t>t1_Levo_cs + t2_Levo_cs + t3_Levo_cs</t>
         </is>
       </c>
     </row>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>iqr_t1_K_cs + iqr_t2_K_cs + iqr_t3_K_cs</t>
+          <t>t1_K_cs + t2_K_cs + t3_K_cs</t>
         </is>
       </c>
     </row>
@@ -3902,7 +3902,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>iqr_t1_Levo_sp + iqr_t2_Levo_sp + iqr_t3_Levo_sp</t>
+          <t>t1_Levo_sp + t2_Levo_sp + t3_Levo_sp</t>
         </is>
       </c>
     </row>
@@ -3939,7 +3939,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>iqr_t1_K_sp + iqr_t2_K_sp + iqr_t3_K_sp</t>
+          <t>t1_K_sp + t2_K_sp + t3_K_sp</t>
         </is>
       </c>
     </row>
